--- a/artfynd/A 12905-2025 artfynd.xlsx
+++ b/artfynd/A 12905-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124288664</v>
+        <v>124288662</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556258</v>
+        <v>556269</v>
       </c>
       <c r="R3" t="n">
-        <v>6698148</v>
+        <v>6698195</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124288661</v>
+        <v>124288664</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556247</v>
+        <v>556258</v>
       </c>
       <c r="R4" t="n">
-        <v>6698150</v>
+        <v>6698148</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124288662</v>
+        <v>124288661</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556269</v>
+        <v>556247</v>
       </c>
       <c r="R5" t="n">
-        <v>6698195</v>
+        <v>6698150</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 12905-2025 artfynd.xlsx
+++ b/artfynd/A 12905-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124288676</v>
+        <v>124288662</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556249</v>
+        <v>556269</v>
       </c>
       <c r="R2" t="n">
-        <v>6698236</v>
+        <v>6698195</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124288662</v>
+        <v>124288676</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556269</v>
+        <v>556249</v>
       </c>
       <c r="R3" t="n">
-        <v>6698195</v>
+        <v>6698236</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124288664</v>
+        <v>124288661</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556258</v>
+        <v>556247</v>
       </c>
       <c r="R4" t="n">
-        <v>6698148</v>
+        <v>6698150</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124288661</v>
+        <v>124288664</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556247</v>
+        <v>556258</v>
       </c>
       <c r="R5" t="n">
-        <v>6698150</v>
+        <v>6698148</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 12905-2025 artfynd.xlsx
+++ b/artfynd/A 12905-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124288662</v>
+        <v>124288664</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556269</v>
+        <v>556258</v>
       </c>
       <c r="R2" t="n">
-        <v>6698195</v>
+        <v>6698148</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124288676</v>
+        <v>124288662</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556249</v>
+        <v>556269</v>
       </c>
       <c r="R3" t="n">
-        <v>6698236</v>
+        <v>6698195</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124288661</v>
+        <v>124288676</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556247</v>
+        <v>556249</v>
       </c>
       <c r="R4" t="n">
-        <v>6698150</v>
+        <v>6698236</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124288664</v>
+        <v>124288661</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556258</v>
+        <v>556247</v>
       </c>
       <c r="R5" t="n">
-        <v>6698148</v>
+        <v>6698150</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 12905-2025 artfynd.xlsx
+++ b/artfynd/A 12905-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124288662</v>
+        <v>124288661</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556269</v>
+        <v>556247</v>
       </c>
       <c r="R3" t="n">
-        <v>6698195</v>
+        <v>6698150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124288661</v>
+        <v>124288662</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556247</v>
+        <v>556269</v>
       </c>
       <c r="R5" t="n">
-        <v>6698150</v>
+        <v>6698195</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 12905-2025 artfynd.xlsx
+++ b/artfynd/A 12905-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124288664</v>
+        <v>124288661</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556258</v>
+        <v>556247</v>
       </c>
       <c r="R2" t="n">
-        <v>6698148</v>
+        <v>6698150</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124288661</v>
+        <v>124288676</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556247</v>
+        <v>556249</v>
       </c>
       <c r="R3" t="n">
-        <v>6698150</v>
+        <v>6698236</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124288676</v>
+        <v>124288662</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556249</v>
+        <v>556269</v>
       </c>
       <c r="R4" t="n">
-        <v>6698236</v>
+        <v>6698195</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124288662</v>
+        <v>124288664</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556269</v>
+        <v>556258</v>
       </c>
       <c r="R5" t="n">
-        <v>6698195</v>
+        <v>6698148</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 12905-2025 artfynd.xlsx
+++ b/artfynd/A 12905-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124288661</v>
+        <v>124288676</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556247</v>
+        <v>556249</v>
       </c>
       <c r="R2" t="n">
-        <v>6698150</v>
+        <v>6698236</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124288676</v>
+        <v>124288664</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556249</v>
+        <v>556258</v>
       </c>
       <c r="R3" t="n">
-        <v>6698236</v>
+        <v>6698148</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124288664</v>
+        <v>124288661</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556258</v>
+        <v>556247</v>
       </c>
       <c r="R5" t="n">
-        <v>6698148</v>
+        <v>6698150</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 12905-2025 artfynd.xlsx
+++ b/artfynd/A 12905-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124288664</v>
+        <v>124288661</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556258</v>
+        <v>556247</v>
       </c>
       <c r="R3" t="n">
-        <v>6698148</v>
+        <v>6698150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124288661</v>
+        <v>124288664</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556247</v>
+        <v>556258</v>
       </c>
       <c r="R5" t="n">
-        <v>6698150</v>
+        <v>6698148</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 12905-2025 artfynd.xlsx
+++ b/artfynd/A 12905-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124288661</v>
+        <v>124288664</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556247</v>
+        <v>556258</v>
       </c>
       <c r="R3" t="n">
-        <v>6698150</v>
+        <v>6698148</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124288664</v>
+        <v>124288661</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556258</v>
+        <v>556247</v>
       </c>
       <c r="R5" t="n">
-        <v>6698148</v>
+        <v>6698150</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 12905-2025 artfynd.xlsx
+++ b/artfynd/A 12905-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124288676</v>
+        <v>124288661</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556249</v>
+        <v>556247</v>
       </c>
       <c r="R2" t="n">
-        <v>6698236</v>
+        <v>6698150</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124288664</v>
+        <v>124288676</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556258</v>
+        <v>556249</v>
       </c>
       <c r="R3" t="n">
-        <v>6698148</v>
+        <v>6698236</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124288662</v>
+        <v>124288664</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556269</v>
+        <v>556258</v>
       </c>
       <c r="R4" t="n">
-        <v>6698195</v>
+        <v>6698148</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124288661</v>
+        <v>124288662</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556247</v>
+        <v>556269</v>
       </c>
       <c r="R5" t="n">
-        <v>6698150</v>
+        <v>6698195</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 12905-2025 artfynd.xlsx
+++ b/artfynd/A 12905-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124288661</v>
+        <v>124288662</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556247</v>
+        <v>556269</v>
       </c>
       <c r="R2" t="n">
-        <v>6698150</v>
+        <v>6698195</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124288676</v>
+        <v>124288661</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556249</v>
+        <v>556247</v>
       </c>
       <c r="R3" t="n">
-        <v>6698236</v>
+        <v>6698150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124288664</v>
+        <v>124288676</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556258</v>
+        <v>556249</v>
       </c>
       <c r="R4" t="n">
-        <v>6698148</v>
+        <v>6698236</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124288662</v>
+        <v>124288664</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556269</v>
+        <v>556258</v>
       </c>
       <c r="R5" t="n">
-        <v>6698195</v>
+        <v>6698148</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 12905-2025 artfynd.xlsx
+++ b/artfynd/A 12905-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124288662</v>
+        <v>124288661</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556269</v>
+        <v>556247</v>
       </c>
       <c r="R2" t="n">
-        <v>6698195</v>
+        <v>6698150</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124288661</v>
+        <v>124288676</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556247</v>
+        <v>556249</v>
       </c>
       <c r="R3" t="n">
-        <v>6698150</v>
+        <v>6698236</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124288676</v>
+        <v>124288664</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556249</v>
+        <v>556258</v>
       </c>
       <c r="R4" t="n">
-        <v>6698236</v>
+        <v>6698148</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124288664</v>
+        <v>124288662</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556258</v>
+        <v>556269</v>
       </c>
       <c r="R5" t="n">
-        <v>6698148</v>
+        <v>6698195</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 12905-2025 artfynd.xlsx
+++ b/artfynd/A 12905-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124288661</v>
+        <v>124288662</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556247</v>
+        <v>556269</v>
       </c>
       <c r="R2" t="n">
-        <v>6698150</v>
+        <v>6698195</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124288676</v>
+        <v>124288664</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556249</v>
+        <v>556258</v>
       </c>
       <c r="R3" t="n">
-        <v>6698236</v>
+        <v>6698148</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124288664</v>
+        <v>124288661</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556258</v>
+        <v>556247</v>
       </c>
       <c r="R4" t="n">
-        <v>6698148</v>
+        <v>6698150</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124288662</v>
+        <v>124288676</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556269</v>
+        <v>556249</v>
       </c>
       <c r="R5" t="n">
-        <v>6698195</v>
+        <v>6698236</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
